--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N80_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N80_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.84118423366776</v>
+        <v>9.886692437971011</v>
       </c>
       <c r="D2" t="n">
-        <v>60.83412899563301</v>
+        <v>9.885545961790363</v>
       </c>
       <c r="E2" t="n">
-        <v>3.137456454788275</v>
+        <v>0.5098366739030945</v>
       </c>
       <c r="F2" t="n">
-        <v>4.256780466549917</v>
+        <v>0.691726825814362</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>53.5537267335925</v>
+        <v>8.702480594208781</v>
       </c>
       <c r="D3" t="n">
-        <v>53.20653950370713</v>
+        <v>8.646062669352409</v>
       </c>
       <c r="E3" t="n">
-        <v>3.137456454788275</v>
+        <v>0.5098366739030945</v>
       </c>
       <c r="F3" t="n">
-        <v>4.256780466549917</v>
+        <v>0.691726825814362</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>59.31076353359926</v>
+        <v>9.637999074209882</v>
       </c>
       <c r="D4" t="n">
-        <v>63.17709627518321</v>
+        <v>10.26627814471727</v>
       </c>
       <c r="E4" t="n">
-        <v>3.137456454788275</v>
+        <v>0.5098366739030945</v>
       </c>
       <c r="F4" t="n">
-        <v>4.256780466549917</v>
+        <v>0.691726825814362</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
